--- a/Data/Regression Evidence 2025/Workday_NewHire_Portugal_Regression_PK17.xlsx
+++ b/Data/Regression Evidence 2025/Workday_NewHire_Portugal_Regression_PK17.xlsx
@@ -1,23 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{48E8A61B-F160-4075-BE8E-197F9913C12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BO$16</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="123">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -214,275 +229,269 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10700256</t>
+    <t>420 Recruitment (Gozyb Sosobo (10034456))</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Dorthy</t>
+  </si>
+  <si>
+    <t>Deckow</t>
+  </si>
+  <si>
+    <t>Sr.</t>
+  </si>
+  <si>
+    <t>Landline</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Automation Street Name</t>
+  </si>
+  <si>
+    <t>4000-087</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>Street Address</t>
+  </si>
+  <si>
+    <t>automation@qe.com</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Retail Assistant</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>420 Lisbon - UBBO</t>
+  </si>
+  <si>
+    <t>1.A.1 - Cto 6 Meses- Abertura Loja- RA/SUP-FT (Contratos RA &amp; Supervisores Portugal-Portugal) (Contratos RA &amp; Supervisores Portugal-Portugal)@401</t>
+  </si>
+  <si>
+    <t>5 Dias</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>94 Retail Operatives</t>
+  </si>
+  <si>
+    <t>01 Accessories</t>
+  </si>
+  <si>
+    <t>PT Monthly</t>
+  </si>
+  <si>
+    <t>Pensões-Casado-Dois Tit.-Deficiente</t>
+  </si>
+  <si>
+    <t>312-ENSINO SECUNDARIO TECNICO COMPLEMENTAR</t>
+  </si>
+  <si>
+    <t>Acréscimo excepcional de actividade da empresa</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Sem Termo (FT) - Permanente</t>
+  </si>
+  <si>
+    <t>Defaulted</t>
+  </si>
+  <si>
+    <t>Portugal Retail Assistant</t>
+  </si>
+  <si>
+    <t>Operador de supermercado de 1</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>01/01/1999</t>
+  </si>
+  <si>
+    <t>Guarda</t>
+  </si>
+  <si>
+    <t>Married</t>
+  </si>
+  <si>
+    <t>26/01/2019</t>
+  </si>
+  <si>
+    <t>Social Security Identification Number (NISS)</t>
+  </si>
+  <si>
+    <t>Taxpayer ID Number (NIF)</t>
+  </si>
+  <si>
+    <t>ID Number (Numero de</t>
+  </si>
+  <si>
+    <t>24983028 3AP24</t>
+  </si>
+  <si>
+    <t>BBVAESMM128</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>PT50000201231234567890154</t>
+  </si>
+  <si>
+    <t>Test_2</t>
+  </si>
+  <si>
+    <t>420 Store Management (Rilyv Zisozy (4206015))</t>
+  </si>
+  <si>
+    <t>Itzel</t>
+  </si>
+  <si>
+    <t>Grant</t>
+  </si>
+  <si>
+    <t>Sra.</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Auto 56662231</t>
+  </si>
+  <si>
+    <t>Store Manager</t>
+  </si>
+  <si>
+    <t>92 Retail Management</t>
+  </si>
+  <si>
+    <t>Actividade sazonal ou outra cujo ciclo anual de produção apresente irregularidades decorrentes da natureza estrutural do respectivo mercado, incluindo o abastecimento de matéria-prima</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>24983028 3AP25</t>
   </si>
   <si>
     <t>Passed</t>
-  </si>
-  <si>
-    <t>420 Recruitment (Gozyb Sosobo (10034456))</t>
-  </si>
-  <si>
-    <t>Portugal</t>
-  </si>
-  <si>
-    <t>Lou</t>
-  </si>
-  <si>
-    <t>Runolfsson</t>
-  </si>
-  <si>
-    <t>Sr.</t>
-  </si>
-  <si>
-    <t>Landline</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Automation Street Name</t>
-  </si>
-  <si>
-    <t>4000-087</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>Street Address</t>
-  </si>
-  <si>
-    <t>automation@qe.com</t>
-  </si>
-  <si>
-    <t>New Hire</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>Retail Assistant</t>
-  </si>
-  <si>
-    <t>Full Time</t>
-  </si>
-  <si>
-    <t>420 Lisbon - UBBO</t>
-  </si>
-  <si>
-    <t>1.A.1 - Cto 6 Meses- Abertura Loja- RA/SUP-FT (Contratos RA &amp; Supervisores Portugal-Portugal) (Contratos RA &amp; Supervisores Portugal-Portugal)@401</t>
-  </si>
-  <si>
-    <t>5 Dias</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>94 Retail Operatives</t>
-  </si>
-  <si>
-    <t>01 Accessories</t>
-  </si>
-  <si>
-    <t>PT Monthly</t>
-  </si>
-  <si>
-    <t>Pensões-Casado-Dois Tit.-Deficiente</t>
-  </si>
-  <si>
-    <t>312-ENSINO SECUNDARIO TECNICO COMPLEMENTAR</t>
-  </si>
-  <si>
-    <t>Acréscimo excepcional de actividade da empresa</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Sem Termo (FT) - Permanente</t>
-  </si>
-  <si>
-    <t>Defaulted</t>
-  </si>
-  <si>
-    <t>Portugal Retail Assistant</t>
-  </si>
-  <si>
-    <t>Operador de supermercado de 1</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>01/01/1999</t>
-  </si>
-  <si>
-    <t>Guarda</t>
-  </si>
-  <si>
-    <t>Married</t>
-  </si>
-  <si>
-    <t>26/01/2019</t>
-  </si>
-  <si>
-    <t>Social Security Identification Number (NISS)</t>
-  </si>
-  <si>
-    <t>Taxpayer ID Number (NIF)</t>
-  </si>
-  <si>
-    <t>ID Number (Numero de</t>
-  </si>
-  <si>
-    <t>24983028 3AP06</t>
-  </si>
-  <si>
-    <t>BBVAESMM128</t>
-  </si>
-  <si>
-    <t>Checking</t>
-  </si>
-  <si>
-    <t>PT50000201231234567890154</t>
-  </si>
-  <si>
-    <t>Test_2</t>
-  </si>
-  <si>
-    <t>10700257</t>
-  </si>
-  <si>
-    <t>420 Store Management (Rilyv Zisozy (4206015))</t>
-  </si>
-  <si>
-    <t>Ivory</t>
-  </si>
-  <si>
-    <t>Gerhold</t>
-  </si>
-  <si>
-    <t>Sra.</t>
-  </si>
-  <si>
-    <t>New</t>
-  </si>
-  <si>
-    <t>Auto 83336163</t>
-  </si>
-  <si>
-    <t>Store Manager</t>
-  </si>
-  <si>
-    <t>92 Retail Management</t>
-  </si>
-  <si>
-    <t>Actividade sazonal ou outra cujo ciclo anual de produção apresente irregularidades decorrentes da natureza estrutural do respectivo mercado, incluindo o abastecimento de matéria-prima</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Single</t>
-  </si>
-  <si>
-    <t>24983028 3AP07</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color indexed="12"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="7"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
       <family val="3"/>
-      <sz val="7"/>
-      <name val="Courier New"/>
     </font>
     <font>
+      <sz val="10"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -505,7 +514,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -517,18 +526,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,31 +558,49 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -606,8 +634,8 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -615,7 +643,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -636,7 +664,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -680,9 +708,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -962,9 +994,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BO16"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BO126"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
     <col min="2" max="2" width="72.6328125" customWidth="1"/>
@@ -1034,7 +1066,7 @@
     <col min="67" max="67" width="26.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.4" customHeight="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:67" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1237,426 +1269,426 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="12">
+        <v>10700457</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="E2" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="F2" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="G2" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="18" t="s">
         <v>69</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>71</v>
       </c>
       <c r="I2" s="19">
         <v>234456532</v>
       </c>
       <c r="J2" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="20">
+        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <v>45846</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="O2" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="20">
-        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45821</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="N2" s="21" t="s">
+      <c r="P2" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="Q2" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="R2" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="S2" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="R2" s="22" t="s">
+      <c r="T2" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="U2" s="20">
+        <f t="shared" ref="U2:U3" ca="1" si="1">L2</f>
+        <v>45846</v>
+      </c>
+      <c r="V2" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="23" t="s">
+      <c r="W2" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="U2" s="20">
-        <f t="shared" ref="U2:U3" si="1">L2</f>
-        <v>45821</v>
-      </c>
-      <c r="V2" s="19" t="s">
+      <c r="X2" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="W2" s="24" t="s">
+      <c r="Y2" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="X2" s="22" t="s">
+      <c r="Z2" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="Y2" s="25" t="s">
+      <c r="AA2" s="26" t="s">
         <v>82</v>
-      </c>
-      <c r="Z2" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA2" s="26" t="s">
-        <v>84</v>
       </c>
       <c r="AB2" s="15">
         <v>40</v>
       </c>
       <c r="AC2" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD2" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE2" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="AD2" s="15" t="s">
+      <c r="AF2" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="AE2" s="20" t="s">
+      <c r="AG2" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="AF2" s="19" t="s">
+      <c r="AH2" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="AG2" s="28" t="s">
+      <c r="AI2" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="AH2" s="19" t="s">
+      <c r="AJ2" s="29" t="s">
         <v>90</v>
-      </c>
-      <c r="AI2" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ2" s="29" t="s">
-        <v>92</v>
       </c>
       <c r="AK2" s="19">
         <v>99</v>
       </c>
       <c r="AL2" s="22">
-        <f t="shared" ref="AL2:AL3" si="2">TODAY()+60</f>
-        <v>45912</v>
+        <f t="shared" ref="AL2:AL3" ca="1" si="2">TODAY()+60</f>
+        <v>45937</v>
       </c>
       <c r="AM2" s="22">
-        <f t="shared" ref="AM2:AM3" si="3">U2</f>
-        <v>45821</v>
+        <f t="shared" ref="AM2:AM3" ca="1" si="3">U2</f>
+        <v>45846</v>
       </c>
       <c r="AN2" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO2" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP2" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="AO2" s="21" t="s">
+      <c r="AQ2" s="20" t="str">
+        <f t="shared" ref="AQ2:AQ3" si="4">AE2</f>
+        <v>N/A</v>
+      </c>
+      <c r="AR2" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="AP2" s="22" t="s">
+      <c r="AS2" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="AQ2" s="20">
-        <f t="shared" ref="AQ2:AQ3" si="4">AE2</f>
-        <v>NaN</v>
-      </c>
-      <c r="AR2" s="15" t="s">
+      <c r="AT2" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AS2" s="15" t="s">
+      <c r="AU2" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV2" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="AT2" s="15" t="s">
+      <c r="AW2" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="AU2" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV2" s="31" t="s">
+      <c r="AX2" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AY2" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="AW2" s="22" t="s">
+      <c r="AZ2" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="AX2" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="AY2" s="31" t="s">
+      <c r="BB2" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="AZ2" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="BA2" s="32" t="s">
+      <c r="BC2" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD2" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="BE2" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="BB2" s="22" t="s">
+      <c r="BF2" s="34">
+        <v>10000895933</v>
+      </c>
+      <c r="BG2" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH2" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="BC2" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="BD2" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BE2" s="33" t="s">
+      <c r="BI2" s="34">
+        <v>100845964</v>
+      </c>
+      <c r="BJ2" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="BK2" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="BF2" s="34">
-        <v>10000895911</v>
-      </c>
-      <c r="BG2" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH2" s="33" t="s">
+      <c r="BL2" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="BI2" s="34">
-        <v>100845944</v>
-      </c>
-      <c r="BJ2" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BK2" s="35" t="s">
+      <c r="BM2" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="BL2" s="36" t="s">
+      <c r="BN2" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="BM2" s="33" t="s">
+      <c r="BO2" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="BN2" s="33" t="s">
+    </row>
+    <row r="3" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="BO2" s="33" t="s">
+      <c r="B3" s="12">
+        <v>10700458</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="3" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="E3" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="G3" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="H3" s="18" t="s">
         <v>113</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>116</v>
       </c>
       <c r="I3" s="19">
         <v>234456532</v>
       </c>
       <c r="J3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="L3" s="20">
+        <f t="shared" ca="1" si="0"/>
+        <v>45846</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N3" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="O3" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L3" s="20">
-        <f t="shared" si="0"/>
-        <v>45821</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="N3" s="21" t="s">
+      <c r="P3" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="Q3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="R3" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="S3" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="Q3" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="R3" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="S3" s="23" t="s">
-        <v>78</v>
-      </c>
       <c r="T3" s="19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="U3" s="20">
-        <f t="shared" si="1"/>
-        <v>45821</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45846</v>
       </c>
       <c r="V3" s="19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="W3" s="24" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="X3" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y3" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z3" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="Y3" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z3" s="22" t="s">
-        <v>83</v>
-      </c>
       <c r="AA3" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AB3" s="15">
         <v>40</v>
       </c>
       <c r="AC3" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD3" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE3" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="AD3" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE3" s="20" t="s">
-        <v>87</v>
-      </c>
       <c r="AF3" s="19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AG3" s="38">
         <v>251</v>
       </c>
       <c r="AH3" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI3" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ3" s="29" t="s">
         <v>90</v>
-      </c>
-      <c r="AI3" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ3" s="29" t="s">
-        <v>92</v>
       </c>
       <c r="AK3" s="19">
         <v>99</v>
       </c>
       <c r="AL3" s="22">
-        <f t="shared" si="2"/>
-        <v>45912</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45937</v>
       </c>
       <c r="AM3" s="22">
-        <f t="shared" si="3"/>
-        <v>45821</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45846</v>
       </c>
       <c r="AN3" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO3" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP3" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="AQ3" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>N/A</v>
+      </c>
+      <c r="AR3" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS3" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT3" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU3" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV3" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="AW3" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="AX3" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AY3" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ3" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA3" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="BB3" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC3" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD3" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="BE3" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="BF3" s="34">
+        <v>10000895934</v>
+      </c>
+      <c r="BG3" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH3" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI3" s="34">
+        <v>100845965</v>
+      </c>
+      <c r="BJ3" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="BK3" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL3" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="AO3" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP3" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="AQ3" s="20">
-        <f t="shared" si="4"/>
-        <v>NaN</v>
-      </c>
-      <c r="AR3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AS3" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT3" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV3" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="AW3" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="AX3" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="AY3" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="AZ3" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="BA3" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="BB3" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="BC3" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="BD3" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BE3" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="BF3" s="34">
-        <v>10000895912</v>
-      </c>
-      <c r="BG3" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH3" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="BI3" s="34">
-        <v>100845945</v>
-      </c>
-      <c r="BJ3" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BK3" s="35" t="s">
+      <c r="BM3" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="BL3" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="BM3" s="33" t="s">
+      <c r="BN3" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="BO3" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="BN3" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="BO3" s="33" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
       <c r="D4" s="14"/>
       <c r="E4" s="15"/>
       <c r="F4" s="16"/>
@@ -1722,10 +1754,10 @@
       <c r="BN4" s="33"/>
       <c r="BO4" s="33"/>
     </row>
-    <row r="5" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="14"/>
       <c r="E5" s="15"/>
       <c r="F5" s="16"/>
@@ -1746,7 +1778,7 @@
       <c r="U5" s="20"/>
       <c r="V5" s="19"/>
       <c r="W5" s="24"/>
-      <c r="X5" s="39"/>
+      <c r="X5" s="40"/>
       <c r="Y5" s="25"/>
       <c r="Z5" s="22"/>
       <c r="AA5" s="26"/>
@@ -1791,10 +1823,10 @@
       <c r="BN5" s="33"/>
       <c r="BO5" s="33"/>
     </row>
-    <row r="6" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="37"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
       <c r="D6" s="14"/>
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
@@ -1859,10 +1891,10 @@
       <c r="BN6" s="33"/>
       <c r="BO6" s="33"/>
     </row>
-    <row r="7" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="37"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
       <c r="D7" s="14"/>
       <c r="E7" s="15"/>
       <c r="F7" s="16"/>
@@ -1928,10 +1960,10 @@
       <c r="BN7" s="33"/>
       <c r="BO7" s="33"/>
     </row>
-    <row r="8" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
       <c r="D8" s="14"/>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -1952,7 +1984,7 @@
       <c r="U8" s="20"/>
       <c r="V8" s="19"/>
       <c r="W8" s="24"/>
-      <c r="X8" s="39"/>
+      <c r="X8" s="40"/>
       <c r="Y8" s="25"/>
       <c r="Z8" s="22"/>
       <c r="AA8" s="26"/>
@@ -1997,10 +2029,10 @@
       <c r="BN8" s="33"/>
       <c r="BO8" s="33"/>
     </row>
-    <row r="9" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="37"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
       <c r="D9" s="14"/>
       <c r="E9" s="15"/>
       <c r="F9" s="16"/>
@@ -2021,7 +2053,7 @@
       <c r="U9" s="20"/>
       <c r="V9" s="19"/>
       <c r="W9" s="24"/>
-      <c r="X9" s="39"/>
+      <c r="X9" s="40"/>
       <c r="Y9" s="25"/>
       <c r="Z9" s="22"/>
       <c r="AA9" s="26"/>
@@ -2066,10 +2098,10 @@
       <c r="BN9" s="33"/>
       <c r="BO9" s="33"/>
     </row>
-    <row r="10" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
       <c r="D10" s="14"/>
       <c r="E10" s="15"/>
       <c r="F10" s="16"/>
@@ -2135,10 +2167,10 @@
       <c r="BN10" s="33"/>
       <c r="BO10" s="33"/>
     </row>
-    <row r="11" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
       <c r="D11" s="14"/>
       <c r="E11" s="15"/>
       <c r="F11" s="16"/>
@@ -2204,10 +2236,10 @@
       <c r="BN11" s="33"/>
       <c r="BO11" s="33"/>
     </row>
-    <row r="12" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
       <c r="D12" s="14"/>
       <c r="E12" s="15"/>
       <c r="F12" s="16"/>
@@ -2273,10 +2305,10 @@
       <c r="BN12" s="33"/>
       <c r="BO12" s="33"/>
     </row>
-    <row r="13" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
       <c r="D13" s="14"/>
       <c r="E13" s="15"/>
       <c r="F13" s="16"/>
@@ -2297,7 +2329,7 @@
       <c r="U13" s="20"/>
       <c r="V13" s="19"/>
       <c r="W13" s="24"/>
-      <c r="X13" s="39"/>
+      <c r="X13" s="40"/>
       <c r="Y13" s="25"/>
       <c r="Z13" s="22"/>
       <c r="AA13" s="26"/>
@@ -2342,10 +2374,10 @@
       <c r="BN13" s="33"/>
       <c r="BO13" s="33"/>
     </row>
-    <row r="14" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
       <c r="D14" s="14"/>
       <c r="E14" s="15"/>
       <c r="F14" s="16"/>
@@ -2411,10 +2443,10 @@
       <c r="BN14" s="33"/>
       <c r="BO14" s="33"/>
     </row>
-    <row r="15" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
       <c r="D15" s="14"/>
       <c r="E15" s="15"/>
       <c r="F15" s="16"/>
@@ -2480,10 +2512,10 @@
       <c r="BN15" s="33"/>
       <c r="BO15" s="33"/>
     </row>
-    <row r="16" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:67" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
       <c r="D16" s="14"/>
       <c r="E16" s="15"/>
       <c r="F16" s="16"/>
@@ -2549,12 +2581,452 @@
       <c r="BN16" s="33"/>
       <c r="BO16" s="33"/>
     </row>
+    <row r="17" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+    </row>
+    <row r="18" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+    </row>
+    <row r="19" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+    </row>
+    <row r="20" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+    </row>
+    <row r="21" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+    </row>
+    <row r="22" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+    </row>
+    <row r="23" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+    </row>
+    <row r="24" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+    </row>
+    <row r="25" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+    </row>
+    <row r="26" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+    </row>
+    <row r="27" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+    </row>
+    <row r="28" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+    </row>
+    <row r="29" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+    </row>
+    <row r="30" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+    </row>
+    <row r="31" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+    </row>
+    <row r="32" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+    </row>
+    <row r="33" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+    </row>
+    <row r="34" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+    </row>
+    <row r="35" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="41"/>
+      <c r="C35" s="41"/>
+    </row>
+    <row r="36" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+    </row>
+    <row r="37" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+    </row>
+    <row r="38" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+    </row>
+    <row r="39" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+    </row>
+    <row r="40" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="41"/>
+      <c r="C40" s="41"/>
+    </row>
+    <row r="41" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+    </row>
+    <row r="42" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="41"/>
+      <c r="C42" s="41"/>
+    </row>
+    <row r="43" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+    </row>
+    <row r="44" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="41"/>
+      <c r="C44" s="41"/>
+    </row>
+    <row r="45" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="41"/>
+      <c r="C45" s="41"/>
+    </row>
+    <row r="46" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="41"/>
+      <c r="C46" s="41"/>
+    </row>
+    <row r="47" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="41"/>
+      <c r="C47" s="41"/>
+    </row>
+    <row r="48" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+    </row>
+    <row r="49" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+    </row>
+    <row r="50" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+    </row>
+    <row r="51" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="41"/>
+      <c r="C51" s="41"/>
+    </row>
+    <row r="52" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="41"/>
+      <c r="C52" s="41"/>
+    </row>
+    <row r="53" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="41"/>
+      <c r="C53" s="41"/>
+    </row>
+    <row r="54" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="41"/>
+      <c r="C54" s="41"/>
+    </row>
+    <row r="55" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="41"/>
+      <c r="C55" s="41"/>
+    </row>
+    <row r="56" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="41"/>
+      <c r="C56" s="41"/>
+    </row>
+    <row r="57" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B57" s="41"/>
+      <c r="C57" s="41"/>
+    </row>
+    <row r="58" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="41"/>
+      <c r="C58" s="41"/>
+    </row>
+    <row r="59" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="41"/>
+      <c r="C59" s="41"/>
+    </row>
+    <row r="60" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="41"/>
+      <c r="C60" s="41"/>
+    </row>
+    <row r="61" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="41"/>
+      <c r="C61" s="41"/>
+    </row>
+    <row r="62" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="41"/>
+      <c r="C62" s="41"/>
+    </row>
+    <row r="63" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+    </row>
+    <row r="64" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B64" s="41"/>
+      <c r="C64" s="41"/>
+    </row>
+    <row r="65" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B65" s="41"/>
+      <c r="C65" s="41"/>
+    </row>
+    <row r="66" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="41"/>
+      <c r="C66" s="41"/>
+    </row>
+    <row r="67" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B67" s="41"/>
+      <c r="C67" s="41"/>
+    </row>
+    <row r="68" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B68" s="41"/>
+      <c r="C68" s="41"/>
+    </row>
+    <row r="69" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+    </row>
+    <row r="70" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B70" s="41"/>
+      <c r="C70" s="41"/>
+    </row>
+    <row r="71" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+    </row>
+    <row r="72" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B72" s="41"/>
+      <c r="C72" s="41"/>
+    </row>
+    <row r="73" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="41"/>
+      <c r="C73" s="41"/>
+    </row>
+    <row r="74" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="41"/>
+      <c r="C74" s="41"/>
+    </row>
+    <row r="75" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B75" s="41"/>
+      <c r="C75" s="41"/>
+    </row>
+    <row r="76" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B76" s="41"/>
+      <c r="C76" s="41"/>
+    </row>
+    <row r="77" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B77" s="41"/>
+      <c r="C77" s="41"/>
+    </row>
+    <row r="78" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B78" s="41"/>
+      <c r="C78" s="41"/>
+    </row>
+    <row r="79" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+    </row>
+    <row r="80" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B80" s="41"/>
+      <c r="C80" s="41"/>
+    </row>
+    <row r="81" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="41"/>
+      <c r="C81" s="41"/>
+    </row>
+    <row r="82" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B82" s="41"/>
+      <c r="C82" s="41"/>
+    </row>
+    <row r="83" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B83" s="41"/>
+      <c r="C83" s="41"/>
+    </row>
+    <row r="84" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B84" s="41"/>
+      <c r="C84" s="41"/>
+    </row>
+    <row r="85" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="41"/>
+      <c r="C85" s="41"/>
+    </row>
+    <row r="86" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B86" s="41"/>
+      <c r="C86" s="41"/>
+    </row>
+    <row r="87" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B87" s="41"/>
+      <c r="C87" s="41"/>
+    </row>
+    <row r="88" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="41"/>
+      <c r="C88" s="41"/>
+    </row>
+    <row r="89" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B89" s="41"/>
+      <c r="C89" s="41"/>
+    </row>
+    <row r="90" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B90" s="41"/>
+      <c r="C90" s="41"/>
+    </row>
+    <row r="91" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B91" s="41"/>
+      <c r="C91" s="41"/>
+    </row>
+    <row r="92" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="41"/>
+      <c r="C92" s="41"/>
+    </row>
+    <row r="93" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B93" s="41"/>
+      <c r="C93" s="41"/>
+    </row>
+    <row r="94" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B94" s="41"/>
+      <c r="C94" s="41"/>
+    </row>
+    <row r="95" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B95" s="41"/>
+      <c r="C95" s="41"/>
+    </row>
+    <row r="96" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B96" s="41"/>
+      <c r="C96" s="41"/>
+    </row>
+    <row r="97" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B97" s="41"/>
+      <c r="C97" s="41"/>
+    </row>
+    <row r="98" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B98" s="41"/>
+      <c r="C98" s="41"/>
+    </row>
+    <row r="99" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B99" s="41"/>
+      <c r="C99" s="41"/>
+    </row>
+    <row r="100" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B100" s="41"/>
+      <c r="C100" s="41"/>
+    </row>
+    <row r="101" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="41"/>
+      <c r="C101" s="41"/>
+    </row>
+    <row r="102" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B102" s="41"/>
+      <c r="C102" s="41"/>
+    </row>
+    <row r="103" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B103" s="41"/>
+      <c r="C103" s="41"/>
+    </row>
+    <row r="104" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B104" s="41"/>
+      <c r="C104" s="41"/>
+    </row>
+    <row r="105" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B105" s="41"/>
+      <c r="C105" s="41"/>
+    </row>
+    <row r="106" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B106" s="41"/>
+      <c r="C106" s="41"/>
+    </row>
+    <row r="107" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B107" s="41"/>
+      <c r="C107" s="41"/>
+    </row>
+    <row r="108" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="41"/>
+      <c r="C108" s="41"/>
+    </row>
+    <row r="109" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B109" s="41"/>
+      <c r="C109" s="41"/>
+    </row>
+    <row r="110" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B110" s="41"/>
+      <c r="C110" s="41"/>
+    </row>
+    <row r="111" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B111" s="41"/>
+      <c r="C111" s="41"/>
+    </row>
+    <row r="112" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B112" s="41"/>
+      <c r="C112" s="41"/>
+    </row>
+    <row r="113" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B113" s="41"/>
+      <c r="C113" s="41"/>
+    </row>
+    <row r="114" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B114" s="41"/>
+      <c r="C114" s="41"/>
+    </row>
+    <row r="115" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B115" s="41"/>
+      <c r="C115" s="41"/>
+    </row>
+    <row r="116" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B116" s="41"/>
+      <c r="C116" s="41"/>
+    </row>
+    <row r="117" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B117" s="41"/>
+      <c r="C117" s="41"/>
+    </row>
+    <row r="118" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="41"/>
+      <c r="C118" s="41"/>
+    </row>
+    <row r="119" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="41"/>
+      <c r="C119" s="41"/>
+    </row>
+    <row r="120" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="41"/>
+      <c r="C120" s="41"/>
+    </row>
+    <row r="121" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B121" s="41"/>
+      <c r="C121" s="41"/>
+    </row>
+    <row r="122" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B122" s="41"/>
+      <c r="C122" s="41"/>
+    </row>
+    <row r="123" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B123" s="41"/>
+      <c r="C123" s="41"/>
+    </row>
+    <row r="124" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="41"/>
+      <c r="C124" s="41"/>
+    </row>
+    <row r="125" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B125" s="41"/>
+      <c r="C125" s="41"/>
+    </row>
+    <row r="126" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B126" s="41"/>
+      <c r="C126" s="41"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1"/>
-    <hyperlink ref="S3" r:id="rId2"/>
+    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>